--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.159.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Note.â€”The folio consists of 100 words...</t>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”The folio consists of 100 words.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L9: isolated marker/symbol line :: 152</t>
@@ -618,12 +622,12 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L18: symbol-only separator/garbage line :: .5 0</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]152</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Note.â€”The folio consists of 100 words...</t>
+          <t>L6: punctuation artifact: repeated periods :: Note.—The folio consists of 100 words...</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€” See Orders of 1850, under which ple</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Office Copyâ€¢</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Office Copy•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: #</t>
+          <t>L18: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -731,12 +735,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œspecial applications for summary</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+79CD CJK UNIFIED IDEOGRAPH-79CD | isolated marker/symbol line :: 种</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See Orders of 1850,under which pleadings need not</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -748,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L99: symbol-only separator/garbage line :: 0 6</t>
+          <t>L86: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -774,12 +778,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -790,14 +794,10 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€� for summary reference, under</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”It is submitted that, although it has not been done</t>
-        </is>
-      </c>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: .</t>
+          <t>L99: symbol-only separator/garbage line :: 0 6</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -849,14 +849,10 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 13</t>
+          <t>L116: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -904,7 +900,7 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç§�</t>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr"/>
@@ -917,7 +913,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L118: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -955,7 +951,7 @@
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+70B9 CJK UNIFIED IDEOGRAPH-70B9 | isolated marker/symbol line :: 点</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr"/>
@@ -968,7 +964,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: I</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1015,7 +1011,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: %</t>
+          <t>L124: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1060,7 +1056,11 @@
           <t>L22: isolated marker/symbol line :: 0</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: Â·</t>
+          <t>L33: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 1</t>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: ，</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 0</t>
+          <t>L72: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L75: symbol-only separator/garbage line :: 1 0</t>
+          <t>L73: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 1</t>
+          <t>L75: symbol-only separator/garbage line :: 1 0</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1637,7 +1637,7 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 0</t>
+          <t>L76: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 0</t>
+          <t>L77: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 6</t>
+          <t>L79: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 1</t>
+          <t>L80: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: .</t>
+          <t>L81: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 5</t>
+          <t>L82: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 0</t>
+          <t>L83: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: p</t>
+          <t>L84: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L93: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: Â·</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -1947,7 +1947,7 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç§�</t>
+          <t>L105: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: C</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+79CD CJK UNIFIED IDEOGRAPH-79CD | isolated marker/symbol line :: 种</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 0</t>
+          <t>L111: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: .</t>
+          <t>L112: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: .</t>
+          <t>L120: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2133,7 +2133,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 5</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2164,7 +2164,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 0</t>
+          <t>L122: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 5</t>
+          <t>L123: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 0</t>
+          <t>L124: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: 2</t>
+          <t>L126: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2288,7 +2288,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L129: isolated marker/symbol line :: 6</t>
+          <t>L127: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 0</t>
+          <t>L128: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: 4</t>
+          <t>L129: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L132: isolated marker/symbol line :: 5</t>
+          <t>L130: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: 0</t>
+          <t>L131: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L135: isolated marker/symbol line :: 1</t>
+          <t>L132: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 3</t>
+          <t>L133: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2489,6 +2489,130 @@
       <c r="X53" s="1" t="inlineStr"/>
       <c r="Y53" s="1" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>L135: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr"/>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
+      <c r="L55" s="1" t="inlineStr"/>
+      <c r="M55" s="1" t="inlineStr"/>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr"/>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr"/>
+      <c r="R55" s="1" t="inlineStr"/>
+      <c r="S55" s="1" t="inlineStr"/>
+      <c r="T55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr"/>
+      <c r="V55" s="1" t="inlineStr"/>
+      <c r="W55" s="1" t="inlineStr"/>
+      <c r="X55" s="1" t="inlineStr"/>
+      <c r="Y55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr"/>
+      <c r="B56" s="1" t="inlineStr"/>
+      <c r="C56" s="1" t="inlineStr"/>
+      <c r="D56" s="1" t="inlineStr"/>
+      <c r="E56" s="1" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr"/>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
+      <c r="L56" s="1" t="inlineStr"/>
+      <c r="M56" s="1" t="inlineStr"/>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>L137: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr"/>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr"/>
+      <c r="R56" s="1" t="inlineStr"/>
+      <c r="S56" s="1" t="inlineStr"/>
+      <c r="T56" s="1" t="inlineStr"/>
+      <c r="U56" s="1" t="inlineStr"/>
+      <c r="V56" s="1" t="inlineStr"/>
+      <c r="W56" s="1" t="inlineStr"/>
+      <c r="X56" s="1" t="inlineStr"/>
+      <c r="Y56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr"/>
+      <c r="C57" s="1" t="inlineStr"/>
+      <c r="D57" s="1" t="inlineStr"/>
+      <c r="E57" s="1" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr"/>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
+      <c r="L57" s="1" t="inlineStr"/>
+      <c r="M57" s="1" t="inlineStr"/>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+70B9 CJK UNIFIED IDEOGRAPH-70B9 | isolated marker/symbol line :: 点</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr"/>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr"/>
+      <c r="R57" s="1" t="inlineStr"/>
+      <c r="S57" s="1" t="inlineStr"/>
+      <c r="T57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr"/>
+      <c r="V57" s="1" t="inlineStr"/>
+      <c r="W57" s="1" t="inlineStr"/>
+      <c r="X57" s="1" t="inlineStr"/>
+      <c r="Y57" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
